--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484566_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484566_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.099500000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.531</v>
+        <v>8.1358</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5685</v>
+        <v>1.4942</v>
       </c>
       <c r="G2" t="n">
         <v>6.2508</v>
@@ -610,13 +610,13 @@
         <v>2.0158</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1707</v>
+        <v>0.7012</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1666</v>
+        <v>0.4382</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3373</v>
+        <v>0.263</v>
       </c>
       <c r="V2" t="n">
         <v>1.5785</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2132</v>
+        <v>4.6772</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7049</v>
+        <v>3.5405</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5083</v>
+        <v>1.1367</v>
       </c>
       <c r="G3" t="n">
         <v>4.4444</v>
@@ -688,13 +688,13 @@
         <v>1.8326</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4023</v>
+        <v>0.8663</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5845</v>
+        <v>0.4201</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8178</v>
+        <v>0.4462</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6335</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2084</v>
+        <v>3.7253</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2632</v>
+        <v>3.6068</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0548</v>
+        <v>0.1186</v>
       </c>
       <c r="G4" t="n">
         <v>4.3575</v>
@@ -766,13 +766,13 @@
         <v>1.0995</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4161</v>
+        <v>0.1009</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3303</v>
+        <v>0.0132</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0858</v>
+        <v>0.0877</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9973</v>
+        <v>3.3903</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8651</v>
+        <v>4.2086</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8678</v>
+        <v>-0.8183</v>
       </c>
       <c r="G5" t="n">
         <v>4.2757</v>
@@ -844,13 +844,13 @@
         <v>1.4661</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2784</v>
+        <v>0.1146</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3854</v>
+        <v>-0.0418</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1069</v>
+        <v>0.1565</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6335</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4964</v>
+        <v>2.4064</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1464</v>
+        <v>1.8335</v>
       </c>
       <c r="F6" t="n">
-        <v>0.35</v>
+        <v>0.5729</v>
       </c>
       <c r="G6" t="n">
         <v>2.1177</v>
@@ -922,13 +922,13 @@
         <v>2.0158</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8046</v>
+        <v>0.1054</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.0837</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0339</v>
+        <v>0.1891</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4722</v>
+        <v>1.5217</v>
       </c>
       <c r="E7" t="n">
         <v>1.9621</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4899</v>
+        <v>-0.4404</v>
       </c>
       <c r="G7" t="n">
         <v>0.3947</v>
@@ -1000,13 +1000,13 @@
         <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2053</v>
+        <v>-0.1557</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0401</v>
+        <v>0.0094</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2649</v>
+        <v>1.4581</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3628</v>
+        <v>1.1845</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.098</v>
+        <v>0.2736</v>
       </c>
       <c r="G8" t="n">
         <v>1.131</v>
@@ -1078,13 +1078,13 @@
         <v>2.1991</v>
       </c>
       <c r="S8" t="n">
-        <v>0.118</v>
+        <v>0.3113</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5113</v>
+        <v>0.333</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3933</v>
+        <v>-0.0217</v>
       </c>
       <c r="V8" t="n">
         <v>-1.267</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5845</v>
+        <v>0.013</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0612</v>
+        <v>-1.5831</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6457</v>
+        <v>1.5961</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0891</v>
@@ -1156,13 +1156,13 @@
         <v>2.7489</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7181</v>
+        <v>0.1467</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5113</v>
+        <v>-0.0105</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2068</v>
+        <v>0.1572</v>
       </c>
       <c r="V9" t="n">
         <v>0.9554</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6637</v>
+        <v>-0.999</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9404</v>
+        <v>-0.9536</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2767</v>
+        <v>-0.0454</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1172</v>
@@ -1234,13 +1234,13 @@
         <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4535</v>
+        <v>1.1182</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7496</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7038</v>
+        <v>0.3818</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7069</v>
+        <v>-1.9844</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0126</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7195</v>
+        <v>-2.8186</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1174</v>
@@ -1312,13 +1312,13 @@
         <v>0.3665</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.2613</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3107</v>
+        <v>0.1324</v>
       </c>
       <c r="U11" t="n">
-        <v>0.228</v>
+        <v>0.129</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5785</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6301</v>
+        <v>-2.0634</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4723</v>
+        <v>-1.0047</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1578</v>
+        <v>-1.0587</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1253</v>
@@ -1390,13 +1390,13 @@
         <v>2.0158</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3374</v>
+        <v>0.2293</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1116</v>
+        <v>0.356</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2258</v>
+        <v>-0.1267</v>
       </c>
       <c r="V12" t="n">
         <v>-1.267</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8462</v>
+        <v>-2.6344</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3056</v>
+        <v>-2.0443</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5406</v>
+        <v>-0.5901</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1352</v>
@@ -1468,13 +1468,13 @@
         <v>0.3665</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1612</v>
+        <v>0.0505</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2021</v>
+        <v>0.0592</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0409</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.4895</v>
+        <v>19.1408</v>
       </c>
       <c r="E14" t="n">
-        <v>18.0686</v>
+        <v>19.7203</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5792000000000002</v>
+        <v>-0.5793999999999996</v>
       </c>
       <c r="G14" t="n">
         <v>15.3876</v>
@@ -1546,13 +1546,13 @@
         <v>18.3257</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1984</v>
+        <v>3.85</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5354999999999999</v>
+        <v>2.1873</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6626</v>
+        <v>1.6628</v>
       </c>
       <c r="V14" t="n">
         <v>-2.8456</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9268</v>
+        <v>1.141</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3413</v>
+        <v>0.6297</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5856</v>
+        <v>0.5113</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6941000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>1.4661</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1959</v>
+        <v>0.0183</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4955</v>
+        <v>-0.207</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2996</v>
+        <v>0.2253</v>
       </c>
       <c r="V15" t="n">
         <v>1.267</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LORENTE</t>
+          <t>O. ROIG VALERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3948</v>
+        <v>0.4477</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6286</v>
+        <v>-0.2138</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2338</v>
+        <v>0.6615</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5064</v>
+        <v>-0.0105</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1671</v>
+        <v>0.4063</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6607</v>
+        <v>-0.4167</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4529</v>
+        <v>-0.1859</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7027</v>
+        <v>0.4552</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7501</v>
+        <v>-0.641</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.9465</v>
+        <v>0.1754</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5356</v>
+        <v>-0.0489</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4109</v>
+        <v>0.2243</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8326</v>
+        <v>0.3665</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8326</v>
+        <v>0.3665</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4094</v>
+        <v>0.0916</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2074</v>
+        <v>-0.0279</v>
       </c>
       <c r="U16" t="n">
-        <v>0.202</v>
+        <v>0.1195</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. ROIG VALERO</t>
+          <t>M. POVEDA CASTELLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0776</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4061</v>
+        <v>2.1123</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4837</v>
+        <v>-2.7126</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0105</v>
+        <v>0.0216</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4063</v>
+        <v>1.471</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4167</v>
+        <v>-1.4494</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1859</v>
+        <v>5.2152</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4552</v>
+        <v>4.3559</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.641</v>
+        <v>0.8592</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1754</v>
+        <v>-5.1935</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0489</v>
+        <v>-2.8849</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2243</v>
+        <v>-2.3086</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3665</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3665</v>
+        <v>2.5656</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2784</v>
+        <v>-0.1559</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2202</v>
+        <v>-0.0712</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0582</v>
+        <v>-0.0847</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. POVEDA CASTELLO</t>
+          <t>J. JIMENEZ LORENTE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.6615</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7853</v>
+        <v>0.6671</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8656</v>
+        <v>-1.3286</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0216</v>
+        <v>0.5064</v>
       </c>
       <c r="H18" t="n">
-        <v>1.471</v>
+        <v>1.1671</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4494</v>
+        <v>-0.6607</v>
       </c>
       <c r="J18" t="n">
-        <v>5.2152</v>
+        <v>3.4529</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3559</v>
+        <v>2.7027</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8592</v>
+        <v>0.7501</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.1935</v>
+        <v>-2.9465</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.8849</v>
+        <v>-1.5356</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.3086</v>
+        <v>-1.4109</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0995</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q18" t="n">
         <v>-3.6651</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5656</v>
+        <v>1.8326</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3642</v>
+        <v>0.3531</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6018</v>
+        <v>0.2459</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2377</v>
+        <v>0.1073</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6335</v>
+        <v>0.3115</v>
       </c>
       <c r="W18" t="n">
         <v>0.6335</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5355</v>
+        <v>-0.8954</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7353</v>
+        <v>2.3507</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2709</v>
+        <v>-3.2461</v>
       </c>
       <c r="G19" t="n">
         <v>-3.1176</v>
@@ -1936,13 +1936,13 @@
         <v>2.3823</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5112</v>
+        <v>0.1514</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6765</v>
+        <v>0.2919</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1653</v>
+        <v>-0.1405</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3115</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2366</v>
+        <v>-1.0065</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1615</v>
+        <v>0.4154</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0751</v>
+        <v>-1.4219</v>
       </c>
       <c r="G20" t="n">
         <v>-2.326</v>
@@ -2014,13 +2014,13 @@
         <v>1.8326</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1385</v>
+        <v>0.0916</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8258</v>
+        <v>-0.2489</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6873</v>
+        <v>0.3405</v>
       </c>
       <c r="V20" t="n">
         <v>0.3115</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8551</v>
+        <v>-1.3641</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1869</v>
+        <v>-0.8985</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6681</v>
+        <v>-0.4656</v>
       </c>
       <c r="G21" t="n">
         <v>0.1084</v>
@@ -2092,13 +2092,13 @@
         <v>1.0995</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.958</v>
+        <v>-0.467</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6056</v>
+        <v>-0.3171</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3524</v>
+        <v>-0.1499</v>
       </c>
       <c r="V21" t="n">
         <v>0.6439</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8194</v>
+        <v>-2.8164</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0761</v>
+        <v>-0.02</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8955</v>
+        <v>-2.7964</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8456</v>
@@ -2170,13 +2170,13 @@
         <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2461</v>
+        <v>-0.2432</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1297</v>
+        <v>-0.2259</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1164</v>
+        <v>-0.0174</v>
       </c>
       <c r="V22" t="n">
         <v>-0.0104</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9238</v>
+        <v>-4.2449</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9616</v>
+        <v>-0.4809</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.9622</v>
+        <v>-3.764</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4066</v>
@@ -2248,13 +2248,13 @@
         <v>1.6493</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3339</v>
+        <v>-0.655</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8258</v>
+        <v>-0.345</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5082</v>
+        <v>-0.31</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.438</v>
+        <v>-6.8479</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2713</v>
+        <v>-3.9828</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1668</v>
+        <v>-2.8651</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6238</v>
@@ -2326,13 +2326,13 @@
         <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3323</v>
+        <v>-0.7423</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.046</v>
+        <v>-0.7575</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2864</v>
+        <v>0.0153</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.4894</v>
+        <v>-16.8483</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5792000000000002</v>
+        <v>0.5791999999999993</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.0687</v>
+        <v>-17.4275</v>
       </c>
       <c r="G25" t="n">
         <v>-15.3878</v>
@@ -2395,7 +2395,7 @@
         <v>-15.0694</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.748899999999999</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q25" t="n">
         <v>-18.3257</v>
@@ -2404,13 +2404,13 @@
         <v>15.5768</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.1983</v>
+        <v>-1.5574</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.6629</v>
+        <v>-1.6627</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5356999999999998</v>
+        <v>0.1054</v>
       </c>
       <c r="V25" t="n">
         <v>2.8455</v>
